--- a/VerveStacks_POL_grids_kan50/source_data/VerveStacks_POL.xlsx
+++ b/VerveStacks_POL_grids_kan50/source_data/VerveStacks_POL.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24740796-9F9B-435C-81DB-E8F817DFB82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2A0AA6-4E7B-43C0-924D-4A6366D931A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="38" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="37" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="36" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="35" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="34" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="43" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="42" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="41" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="40" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="39" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -4292,7 +4292,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D775FF2-2EDE-4911-A328-C3461082C90D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B782D861-8B39-4540-89E1-131A571FF37E}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7420,7 +7420,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899CE88A-E367-4955-BC90-5B85D3A0D6F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DC0891-0C88-46EA-8C7A-641FB888FAFB}">
   <dimension ref="B2:L81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10191,7 +10191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABCA1B16-48A5-4CCB-8670-633DA3F15858}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB21886-B7BA-4D2B-B40D-C19DC3099FC2}">
   <dimension ref="B2:J186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15542,7 +15542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29754720-4458-4E1B-A29B-7D58A069A2F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFCF34FC-FEF9-4374-B2C6-B81417DA1A10}">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15987,7 +15987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210F6355-2623-417C-A58D-67F439E2D819}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE865244-8470-4074-B888-ED4CF4B24A9A}">
   <dimension ref="A1:AD529"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41350,7 +41350,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T338">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U338">
         <v>0</v>
@@ -41397,7 +41397,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T339">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U339">
         <v>0</v>
@@ -41444,7 +41444,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T340">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U340">
         <v>0</v>
@@ -41491,7 +41491,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T341">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U341">
         <v>0</v>
@@ -41538,7 +41538,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T342">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U342">
         <v>0</v>
@@ -41585,7 +41585,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T343">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U343">
         <v>0</v>
@@ -41632,7 +41632,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T344">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U344">
         <v>0</v>
@@ -41679,7 +41679,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T345">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U345">
         <v>0</v>
@@ -41726,7 +41726,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T346">
-        <v>0.11560558285760576</v>
+        <v>0.11560558285760573</v>
       </c>
       <c r="U346">
         <v>0</v>
